--- a/pages/猫咪档案.xlsx
+++ b/pages/猫咪档案.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F20607-0B08-4A23-85EB-E655D79AE5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D32A96-32F9-4CAA-BAB8-AD2FFC046C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -377,102 +377,103 @@
     <t>请按照严格按照格式书写</t>
   </si>
   <si>
+    <t>饭饭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿凶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胖橘</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>依依</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>长毛奶牛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玳瑁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>橘猫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯白</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>异瞳小天使</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小乖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小淘</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小橘</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>橘白</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>好看的长毛奶牛 白多 小胡子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吃东西的时候可以摸头</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>简述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>四公寓围栏，妈妈旁边，兄弟姐妹附近</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有点胆小</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>好奇心强，长得像爸爸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小乖小淘小橘的麻麻</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿凶的孩子，爸爸疑似胖橘</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>疑似小乖小淘小橘的爸爸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最近变温柔了，总是骗吃骗喝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>请按照x年x月x日格式填写，并且需要在个位数前加0</t>
-  </si>
-  <si>
-    <t>饭饭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿凶</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>胖橘</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>依依</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>长毛奶牛</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>玳瑁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>橘猫</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>纯白</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>异瞳小天使</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>小乖</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>小淘</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>小橘</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>橘白</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>好看的长毛奶牛 白多 小胡子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>吃东西的时候可以摸头</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>简述</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>四公寓围栏，妈妈旁边，兄弟姐妹附近</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>有点胆小</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>好奇心强，长得像爸爸</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>小乖小淘小橘的麻麻</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿凶的孩子，爸爸疑似胖橘</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>疑似小乖小淘小橘的爸爸</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>最近变温柔了，总是骗吃骗喝</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -806,7 +807,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -979,12 +980,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="57" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1004,30 +1026,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1343,7 +1341,7 @@
     <col min="10" max="10" width="10.375" style="3" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="3"/>
     <col min="12" max="12" width="12.875" style="8" customWidth="1"/>
-    <col min="13" max="13" width="12" style="8" customWidth="1"/>
+    <col min="13" max="13" width="11.125" style="8" customWidth="1"/>
     <col min="14" max="14" width="40.375" style="3" customWidth="1"/>
     <col min="15" max="15" width="8.875" style="3" customWidth="1"/>
     <col min="16" max="16" width="24.375" style="4" customWidth="1"/>
@@ -1385,22 +1383,22 @@
       <c r="A3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="70"/>
+      <c r="C3" s="62"/>
       <c r="D3" s="15"/>
       <c r="E3" s="11"/>
-      <c r="F3" s="66" t="s">
+      <c r="F3" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="67"/>
-      <c r="H3" s="68"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="75"/>
       <c r="I3" s="16"/>
-      <c r="J3" s="71" t="s">
+      <c r="J3" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="72"/>
+      <c r="K3" s="64"/>
       <c r="L3" s="17"/>
       <c r="M3" s="18" t="s">
         <v>19</v>
@@ -1424,7 +1422,7 @@
       <c r="T3" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="U3" s="64" t="s">
+      <c r="U3" s="71" t="s">
         <v>35</v>
       </c>
       <c r="V3" s="14" t="s">
@@ -1475,7 +1473,7 @@
       <c r="T4" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="U4" s="65"/>
+      <c r="U4" s="72"/>
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
       <c r="X4" s="31" t="s">
@@ -1487,20 +1485,20 @@
     </row>
     <row r="5" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="25"/>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="75"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="67"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
-      <c r="H5" s="69" t="s">
+      <c r="H5" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="70"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="62"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" s="33" t="s">
@@ -1518,7 +1516,7 @@
       <c r="T5" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="U5" s="65"/>
+      <c r="U5" s="72"/>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
@@ -1548,7 +1546,7 @@
       <c r="T6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="U6" s="65" t="s">
+      <c r="U6" s="72" t="s">
         <v>36</v>
       </c>
       <c r="V6" s="14" t="s">
@@ -1593,7 +1591,7 @@
       <c r="T7" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="U7" s="65"/>
+      <c r="U7" s="72"/>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
       <c r="X7" s="29">
@@ -1632,7 +1630,7 @@
       <c r="T8" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="U8" s="65" t="s">
+      <c r="U8" s="72" t="s">
         <v>37</v>
       </c>
       <c r="V8" s="11"/>
@@ -1673,7 +1671,7 @@
       <c r="T9" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="U9" s="65"/>
+      <c r="U9" s="72"/>
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
       <c r="X9" s="29">
@@ -1701,7 +1699,7 @@
       <c r="M10" s="17"/>
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
-      <c r="P10" s="62" t="s">
+      <c r="P10" s="69" t="s">
         <v>71</v>
       </c>
       <c r="Q10" s="43"/>
@@ -1740,12 +1738,12 @@
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="17" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="M11" s="17"/>
       <c r="N11" s="11"/>
       <c r="O11" s="11"/>
-      <c r="P11" s="63"/>
+      <c r="P11" s="70"/>
       <c r="Q11" s="47"/>
       <c r="R11" s="11"/>
       <c r="S11" s="11"/>
@@ -1799,7 +1797,7 @@
         <v>39</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O12" s="11" t="s">
         <v>26</v>
@@ -1839,14 +1837,14 @@
         <v>1</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" s="11">
         <v>1</v>
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="59" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G13" s="11">
         <v>3</v>
@@ -1864,13 +1862,13 @@
       <c r="L13" s="50"/>
       <c r="M13" s="17"/>
       <c r="N13" s="51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O13" s="52">
         <v>-1</v>
       </c>
       <c r="P13" s="53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q13" s="12"/>
       <c r="R13" s="11"/>
@@ -1890,14 +1888,14 @@
         <v>2</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" s="11">
         <v>1</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G14" s="12">
         <v>4</v>
@@ -1915,7 +1913,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O14" s="12">
         <v>4</v>
@@ -1923,7 +1921,7 @@
       <c r="P14" s="54"/>
       <c r="Q14" s="12"/>
       <c r="R14" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S14" s="11"/>
       <c r="T14" s="11"/>
@@ -1941,14 +1939,14 @@
         <v>3</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" s="11">
         <v>1</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G15" s="11">
         <v>2</v>
@@ -1972,7 +1970,7 @@
       <c r="P15" s="53"/>
       <c r="Q15" s="12"/>
       <c r="R15" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S15" s="11"/>
       <c r="T15" s="11"/>
@@ -1990,14 +1988,14 @@
         <v>4</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16" s="11">
         <v>1</v>
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G16" s="57">
         <v>5</v>
@@ -2015,7 +2013,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" s="51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O16" s="11">
         <v>-1</v>
@@ -2039,20 +2037,20 @@
         <v>5</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D17" s="11">
         <v>1</v>
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G17" s="11">
         <v>2</v>
       </c>
-      <c r="H17" s="61" t="s">
-        <v>93</v>
+      <c r="H17" s="60" t="s">
+        <v>92</v>
       </c>
       <c r="I17" s="48">
         <v>-1</v>
@@ -2064,11 +2062,11 @@
         <v>0</v>
       </c>
       <c r="L17" s="17"/>
-      <c r="M17" s="60">
-        <v>44378</v>
+      <c r="M17" s="17">
+        <v>202107</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O17" s="55">
         <v>1</v>
@@ -2076,7 +2074,7 @@
       <c r="P17" s="53"/>
       <c r="Q17" s="12"/>
       <c r="R17" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
@@ -2094,20 +2092,20 @@
         <v>6</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D18" s="11">
         <v>1</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G18" s="12">
         <v>2</v>
       </c>
-      <c r="H18" s="61" t="s">
-        <v>93</v>
+      <c r="H18" s="60" t="s">
+        <v>92</v>
       </c>
       <c r="I18" s="48">
         <v>-1</v>
@@ -2119,11 +2117,11 @@
         <v>0</v>
       </c>
       <c r="L18" s="17"/>
-      <c r="M18" s="60">
-        <v>44379</v>
+      <c r="M18" s="17">
+        <v>202107</v>
       </c>
       <c r="N18" s="51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O18" s="55">
         <v>2</v>
@@ -2131,7 +2129,7 @@
       <c r="P18" s="53"/>
       <c r="Q18" s="12"/>
       <c r="R18" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="S18" s="11"/>
       <c r="T18" s="11"/>
@@ -2148,19 +2146,19 @@
         <v>7</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D19" s="11">
         <v>1</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G19">
         <v>2</v>
       </c>
-      <c r="H19" s="61" t="s">
-        <v>93</v>
+      <c r="H19" s="60" t="s">
+        <v>92</v>
       </c>
       <c r="I19" s="48">
         <v>-1</v>
@@ -2171,17 +2169,17 @@
       <c r="K19" s="11">
         <v>0</v>
       </c>
-      <c r="M19" s="60">
-        <v>44380</v>
+      <c r="M19" s="17">
+        <v>202107</v>
       </c>
       <c r="N19" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O19">
         <v>2</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X19" s="11">
         <v>0</v>
@@ -2766,15 +2764,15 @@
   </sheetData>
   <autoFilter ref="A12:T112" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="9">
+    <mergeCell ref="U3:U5"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="H5:K5"/>
     <mergeCell ref="P10:P11"/>
-    <mergeCell ref="U3:U5"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
